--- a/backend/sample_data/mighty_knight_template.xlsx
+++ b/backend/sample_data/mighty_knight_template.xlsx
@@ -1,16 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Coaches" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coaches" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$O$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coaches'!$A$1:$N$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -414,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,17 +500,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STU001</t>
+          <t>MKS00074</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Harshitha</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Beginner 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,41 +524,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>5 pm – 9 pm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>6 pm – 9 pm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>5 pm – 9 pm</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>8 pm – 9 pm</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>5 pm – 9 pm</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>8 pm – 9 pm</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -563,22 +566,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Usually 12 classes. 16 classes needed only for July 2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STU002</t>
+          <t>MKS00095</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ananya Patel</t>
+          <t>Nitharsana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -592,64 +599,63 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STU003</t>
+          <t>MKS00111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rohan Gupta</t>
+          <t>S.V.Kavisree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -663,21 +669,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -687,40 +693,39 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>6 pm – 7 pm</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STU004</t>
+          <t>MKS00112</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diya Iyer</t>
+          <t>Mithun Rajamani chakravarthi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -734,31 +739,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -768,30 +773,29 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STU005</t>
+          <t>MKS00115</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>HAASHINI  SHRIVY V</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -805,11 +809,11 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -819,55 +823,54 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>7 pm – 9 pm</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>7 pm – 9 pm</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>7 pm – 9 pm</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STU006</t>
+          <t>MKS00129</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sanya Malhotra</t>
+          <t>R Muhammad Fahim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -876,11 +879,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -890,7 +893,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -900,17 +903,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>9 pm – 2 pm</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -918,22 +921,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Saturday &amp; Sunday 9am-2pm | Trainer choices: Raveena &gt; Prakash</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STU007</t>
+          <t>MKS00137</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Pragatheeswaran</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -947,31 +954,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -981,30 +988,29 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STU008</t>
+          <t>MKS00140</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Isha Joshi</t>
+          <t>Mithra.M</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basic 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1018,31 +1024,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1052,25 +1058,24 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STU009</t>
+          <t>MKS00142</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aditya Verma</t>
+          <t>Dev dharsan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1080,7 +1085,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1089,64 +1094,63 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STU010</t>
+          <t>MKS00147</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meera Nair</t>
+          <t>yaazhini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Basic 2</t>
+          <t>Beginner 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1160,59 +1164,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STU011</t>
+          <t>MKS00148</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karan Singh</t>
+          <t xml:space="preserve"> N.Charan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1231,69 +1234,68 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STU012</t>
+          <t>MKS00149</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tara Sen</t>
+          <t>A.T.Vagish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Beginner 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1302,16 +1304,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04:00 PM – 06:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>04:00 PM – 06:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1326,7 +1328,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1336,7 +1338,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>09:00 AM – 12:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1344,17 +1346,16 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STU013</t>
+          <t>MKS00150</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Varun Rao</t>
+          <t>P.V Subhiksha</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1364,7 +1365,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1373,69 +1374,73 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>04:00 PM – 06:00 PM</t>
+          <t>5 pm – 6 pm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>04:00 PM – 06:00 PM</t>
+          <t>5 pm – 6 pm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>5 pm – 6 pm</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>5 pm – 6 pm</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>5 pm – 6 pm</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>5 pm – 6 pm</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>09:00 AM – 12:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Trainer choices: no preference</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STU014</t>
+          <t>MKS00153</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nikhil Deshmukh</t>
+          <t>Viraaj Shanmugam</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Beginner 2</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1444,41 +1449,41 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>07:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>07:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>07:00 PM – 09:00 PM</t>
+          <t>7 pm – 8 pm</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>7 pm – 8 pm</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1486,27 +1491,31 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sunday anytime, preferrably 9am | Trainer choices: Guru mam &gt; Raveena &gt; Abinaya</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STU015</t>
+          <t>MKS00154</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prisha Kapoor</t>
+          <t>H V Kanishk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Beginner 3</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1515,41 +1524,41 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>05:00 PM – 07:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>05:00 PM – 07:00 PM</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>No Preference</t>
+          <t>5 pm – 9 pm</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>5 pm – 9 pm</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09:00 AM – 01:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1557,22 +1566,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Skating class from Monday to thursday 6.30pm to 8.30pm</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STU016</t>
+          <t>MKS00155</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Devansh Saxena</t>
+          <t>S. Thashwin Raj</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Early Intermediate 1</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1586,69 +1599,68 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>06:00 PM – 08:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>05:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STU017</t>
+          <t>MKS00157</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Riya Banerjee</t>
+          <t>S.P.NEHASRI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Early Intermediate 2</t>
+          <t>Basic 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1657,31 +1669,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>07:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>07:00 PM – 09:00 PM</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1691,96 +1703,6303 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Individual training request</t>
+          <t>one weekday, one saturday and one Sunday needed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STU018</t>
+          <t>MKS00159</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vihaan Agarwal</t>
+          <t>Viraline A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Basic 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MKS00161</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mithra sree</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MKS00168</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vikash</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Basic 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MKS00169</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KH Amrith</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MKS00170</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aadhav Mithun</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Basic 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1 pm – 5 pm</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Weekly 1 class, Saturday only</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MKS00171</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nishwanth R</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Basic 2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MKS00172</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A R Thatchiraa Shree</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MKS00175</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sarvesh K</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MKS00176</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D R RAJAGOPALAN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MKS00177</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jasra J</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Basic 1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sunday 9am only preferred | Trainer choices: Bathrinath &gt; Raveena</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MKS00178</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ridhanya Sri.V</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Basic 2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>12</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MKS00181</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Thiyashwar S</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Basic 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MKS00184</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kaashvi Prakash</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Basic 1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Only1 class per week on Wednesday | Trainer choices: Raveena</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MKS00007</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ryan Stalin </t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>12</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MKS00020</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M Nethran</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>12</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MKS00023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kavinpriyan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>12</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MKS00038</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Oviya B</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MKS00039</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S. YASWANNTH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>12</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Need only 8 classes per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MKS00048</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kirthik</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6 am – 7 am</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6 am – 7 am</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>in IST | Trainer choices: no preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MKS00052</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Thiyaneshwaran</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>12</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MKS00055</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N.sri dharshni</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>pm-</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sunday preferred timing at 1.30pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MKS00063</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rithu Ashwika</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>12</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MKS00066</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Anikha</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8 am to 12 pm</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Saturday1 class &amp; Sunday tournament</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MKS00067</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Akshadhasree</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10 am – 12 pm</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Saturday1 class &amp; Sunday tournament</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MKS00069</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Isha</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sunday preferred timing at 1.30pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MKS00073</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Harini</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MKS00075</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Jovinya</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>14</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sunday preferred timing at 1.30pm | Trainer choices: Raveena &gt; Guru &gt; Abinaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MKS00076</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Syed Individual</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Trainer choices: Raveena</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MKS00079</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D KAVISH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>12</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MKS00092</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ayaan Haris</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>12</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MKS00098</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>B.AARAV NARAYAN</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>12</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MKS00100</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MELWIN G</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>12</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MKS00101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M. R. Darshan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>12</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MKS00107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Yuviga</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>12</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MKS00108</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>B SARVESSH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>12</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MKS00110</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>V. Dhaksha</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>7 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Trainer choices: Raveena</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MKS00114</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dhanya
+  sri S S </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>12</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MKS00118</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M.Nalini Hirthika</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>12</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MKS00121</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>M.kanshika sai</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MKS00122</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rethushana. R</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>12</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MKS00127</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D. Tharun</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MKS00130</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Vishvin.B</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>12</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MKS00131</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>V. Srikaviyazhini</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MKS00134</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Haricharan N.U</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MKS00138</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>waseem</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>12</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MKS00141</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Alagu Durai</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>9 am – 10 am</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Trainer choices: no preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MKS00143</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pranith</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>12</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MKS00156</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pugazhini Navaneethan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6 am – 7 am</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>6 am – 7 am</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>in IST | Trainer choices: no preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MKS00160</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sidharth</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>12</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MKS00162</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Priyan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Usa</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6 am – 7 am</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>6 am – 7 am</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>in IST | Trainer choices: no preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MKS00163</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Charvi</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>12</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MKS00164</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaibhavi Krishna </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>9</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Vaishnavi krishna &amp; Vaibhavi krishna is a special batch for only both-8 classes per month,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MKS00165</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaishnavi Krishna </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>9</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MKS00166</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>M VARUNESH PANDI</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>8 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MKS00173</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>V.Pranav</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>12</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MKS00174</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Avyukt A Praveen</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>5 pm – 6 pm</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MKS00179</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sanjay Karthik.D</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>12</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>5 pm – 6 pm</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5 pm – 6 pm</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>5 pm – 6 pm</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MKS00180</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Rogan Siddharth</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>12</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>5 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MKS00182</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Samuel Rajan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Beginner 3</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>12</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>adult, to combine with Manikandan S</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MKS00183</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Manikandan S</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>12</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>6 pm – 8 pm</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>adult, to combine with Samuel Rajan</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MKS00185</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Nirupan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Beginner 1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>12</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MKS00004</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sherwin vijay v</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>12</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Sunday tournament should be replaced to intermediate tournament on Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MKS00009</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S.Raagavarshenee</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Early Intermediate 1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>12</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MKS00014</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hitesh prabu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>12</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MKS00024</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Diya</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>12</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MKS00025</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nandabalan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>12</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MKS00034</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shakthivishakan A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Early Intermediate 1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>12</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MKS00049</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Reyhan nawaz</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>12</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MKS00054</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Nithesh Nagarathinam</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Early Intermediate 1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>24</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Monthly 24 classes of Limited batch at Early Intermediate level | Trainer choices: Dhaanush &gt; Prakash</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MKS00070</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sanjumithra</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Early Intermediate 1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>12</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MKS00072</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Arishmithran</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Early Intermediate 1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>12</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MKS00091</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pradhiyuksha</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Early Intermediate 1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>12</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MKS00093</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>V.Dharmasastha Individual</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Trainer choices: Dhaanush</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MKS00094</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sai Dhushvanth</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MKS00102</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Vedhanth V</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>12</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MKS00113</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>M.Nishik</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>12</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MKS00126</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S NALLADHITHIYA </t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Early Intermediate 2</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>12</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MKS00018</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>K.K.ANUSHRI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>12</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MKS00037</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Krishiv Ajay</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>12</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MKS00045</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Srikavi Bharathi</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>12</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MKS00050</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ineya Individual</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>IST</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>08:00 PM – 09:00 PM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>08:00 PM – 09:00 PM</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>08:00 PM – 09:00 PM</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>07:00 PM – 09:00 PM</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>6</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>6 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Master preparation batch</t>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Trainer choices: Prakash</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MKS00053</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Vivaan Aaditya</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>12</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>7 pm – 9 pm</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Trainer choices: Arshath &gt; Dhaanush</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MKS00132</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Sai Eswar</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>17</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>8.30 pm – 10 pm</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Sunday 9am-1pm available | Trainer choices: Dhaanush &gt; Prakash &gt; Saravanan</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MKS00167</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Selvakrishna RK</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>12</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MKS00186</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>M.Srisaran</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Basic 1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>12</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MKS00187</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Anisha. D</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Basic 2</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>12</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MKS00188</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>R.Kavya prithiyangara</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Beginner 2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>12</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MKS00189</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BHAANAVI.V</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Basic 1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>12</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No Preference</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1869,125 +8088,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Guruvanthana</t>
+          <t>Raveena</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1</t>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>60 - 90</t>
+          <t>60-90</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>8am-3pm</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Evening (4 PM - 9 PM)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Primary lead for Beginner batches</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Monday: 5 pm – 9 pm (max 3); Tuesday: 5 pm – 6 pm, 7 pm – 8 pm (max 1); Wednesday: 5 pm – 9 pm (max 3); Thursday: 5 pm – 9 pm (max 3); Friday: 5 pm – 6 pm, 7 pm – 8 pm (max 1); Saturday: 6 am – 7 am, 9 am – 2 pm, 4 pm – 9 pm (max 5)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhaanush</t>
+          <t>Guruvanthana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1, Early Intermediate 2, Intermediate</t>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>70 - 78</t>
+          <t>35-40</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No Sunday Tournaments</t>
+          <t>8am-3pm</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Midday &amp; Evening</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Avoid Sunday tournament assignments</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Monday: 6 pm – 9 pm (max 1); Tuesday: 6 pm – 7 pm, 8 pm – 9 pm (max 1); Wednesday: 6 pm – 9 pm (max 1); Thursday: Not available (max 0); Friday: 6 pm – 9 pm (max 2); Saturday: 6 pm – 9 pm (max 2)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshath</t>
+          <t>Dhaanush</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Early Intermediate 2, Intermediate</t>
+          <t>Beginner 2, Beginner 3, Early Intermediate 1, Early Intermediate 2, Intermediate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35 - 40</t>
+          <t>70-78</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2006,140 +8213,132 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>8am-3pm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Evening (6 PM - 9 PM)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Senior Master Coach for Intermediate levels</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>Monday: 4 pm – 10 pm (max 3); Tuesday: 4 pm – 10 pm (max 3); Wednesday: 4 pm – 10 pm (max 3); Thursday: 4 pm – 10 pm (max 3); Friday: 4 pm – 10 pm (max 3); Saturday: 4 pm – 10 pm (max 3)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Will go to tournament on 4,5,6th july, only available after 7pm for only 2 classes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saravanan</t>
+          <t>Arshath</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beginner 2, Beginner 3, Early Intermediate 1, Intermediate</t>
+          <t>Early Intermediate 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30 - 60</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No Sunday Tournaments</t>
+          <t>8am-3pm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Monday: Not available (max 0); Tuesday: Not available (max 0); Wednesday: Not available (max 0); Thursday: Not available (max 0); Friday: Not available (max 0); Saturday: 5 pm – 9 pm (max 3)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Avoid Sunday tournament assignments</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>Maybe monthly 2-5 classes can be scheduled in weekday evening after 6pm</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bathrinath</t>
+          <t>Saravanan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1, Beginner 2</t>
+          <t>Early Intermediate 1, Early Intermediate 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60 - 90</t>
+          <t>0-8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>No Preference</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Morning &amp; Evening</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Top Priority for Basic levels</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>Monday: 6 pm – 9 pm (max 1); Tuesday: 6 pm – 9 pm (max 1); Wednesday: 6 pm – 9 pm (max 1); Thursday: 6 pm – 9 pm (max 1); Friday: 6 pm – 9 pm (max 1); Saturday: 6 pm – 9 pm (max 1)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Abinaya</t>
+          <t>bathrinath</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2149,156 +8348,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30 - 60</t>
+          <t>30-60</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>8am-3pm</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Morning (6 AM - 8 AM) &amp; Evening</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Available for early morning slots</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>Monday: 6 am – 8 am, 6 pm – 9 pm (max 2); Tuesday: 6 am – 8 am, 6 pm – 9 pm (max 2); Wednesday: 6 am – 8 am, 6 pm – 9 pm (max 2); Thursday: 6 am – 8 am, 6 pm – 9 pm (max 2); Friday: 6 am – 8 am, 6 pm – 9 pm (max 2); Saturday: 6 am – 8 am, 6 pm – 9 pm (max 2)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prakash</t>
+          <t>Abinaya</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1, Early Intermediate 2, Intermediate</t>
+          <t>Basic 1, Basic 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30 - 100</t>
+          <t>30-60</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>8am-3pm</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All Operating Hours</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Versatile Coach across all levels</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Monday: 6 am – 10 am, 7 pm – 9 pm (max 2); Tuesday: 6 am – 10 am, 7 pm – 9 pm (max 2); Wednesday: 6 am – 10 am, 7 pm – 9 pm (max 2); Thursday: 6 am – 10 am, 7 pm – 9 pm (max 2); Friday: 6 am – 10 am, 7 pm – 9 pm (max 2); Saturday: 6 am – 10 am, 4 pm – 9 pm (max 3)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manikandan</t>
+          <t>Prakash</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1</t>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1, Early Intermediate 2, Intermediate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16 - 20</t>
+          <t>30-100</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>8am-2pm</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Monday: 6 am – 10 am, 4 pm – 9 pm (max 5); Tuesday: 6 am – 10 am, 4 pm – 9 pm (max 5); Wednesday: 6 am – 10 am, 4 pm – 9 pm (max 5); Thursday: 6 am – 10 am, 4 pm – 9 pm (max 5); Friday: 6 am – 10 am, 4 pm – 9 pm (max 5); Saturday: 6 am – 10 am, 4 pm – 9 pm (max 5)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Part-time Coach</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>Should be considered only as substitute or special classes or makeup classes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/sample_data/mighty_knight_template.xlsx
+++ b/backend/sample_data/mighty_knight_template.xlsx
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Beginner 3</t>
+          <t>Beginner 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Intermediate 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1</t>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Early Intermediate 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1, Early Intermediate 2, Intermediate</t>
+          <t>Beginner 1, Beginner 2, Early Intermediate 1, Early Intermediate 2, Intermediate 1, Intermediate 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Early Intermediate 2, Intermediate</t>
+          <t>Early Intermediate 2, Intermediate 1, Intermediate 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beginner 2, Beginner 3, Early Intermediate 1, Intermediate</t>
+          <t>Beginner 2, Early Intermediate 1, Intermediate 1, Intermediate 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Beginner 3, Early Intermediate 1, Early Intermediate 2, Intermediate</t>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Early Intermediate 1, Early Intermediate 2, Intermediate 1, Intermediate 2, Advanced</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/backend/sample_data/mighty_knight_template.xlsx
+++ b/backend/sample_data/mighty_knight_template.xlsx
@@ -1791,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1869,7 +1869,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Guruvanthana</t>
+          <t>GURU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhaanush</t>
+          <t>DHAANUSH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1977,7 +1977,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshath</t>
+          <t>ARSHATH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saravanan</t>
+          <t>SARAVANAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bathrinath</t>
+          <t>BATHRI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Abinaya</t>
+          <t>ABINAYA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2193,7 +2193,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prakash</t>
+          <t>PRAKASH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2247,7 +2247,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manikandan</t>
+          <t>MANIKANDAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2297,6 +2297,60 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HEMA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Tournament</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20 - 40</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Tournament only</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/sample_data/mighty_knight_template.xlsx
+++ b/backend/sample_data/mighty_knight_template.xlsx
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Early Intermediate 1, Early Intermediate 2, Intermediate 1, Intermediate 2, Advanced</t>
+          <t>Basic 1, Basic 2, Beginner 1, Beginner 2, Early Intermediate 1, Early Intermediate 2, Intermediate 1, Intermediate 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
